--- a/FINAL_SUBMISSION/02_市场观察/02_市场观察记录.xlsx
+++ b/FINAL_SUBMISSION/02_市场观察/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -550,6 +550,110 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>3932.70（+0.07%）</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>13774.91（+1.91%）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>4575.02（+0.59%）</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>8979亿元</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>印制电路板(7.62%)、元件(6.72%)、种子(6.35%)、其他种植业(6.13%)、通信网络设备及器件(5.44%)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>被动元件(4.42%)、半导体设备(4.4%)、其他养殖(4.36%)、激光设备(4.16%)、海洋捕捞(4.09%)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4575.02点（+0.59%），跌破20日均线；两市成交额约8979亿元，较前5日均量萎缩（前5日均值约9104亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为印制电路板、元件、种子，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3940.55（+0.20%）</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>13703.21（-0.52%）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4558.74（-0.36%）</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9156亿元</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>粮食种植(7.8%)、房产租赁经纪(7.53%)、磷肥及磷化工(7.01%)、其他农产品加工(6.95%)、学历教育(6.84%)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>油田服务(5.0%)、煤化工(4.89%)、油服工程(4.72%)、农产品加工(4.69%)、其他种植业(4.65%)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4558.74点（-0.36%），跌破20日均线；两市成交额约9156亿元，较前5日均量放大（前5日均值约8871亿元），市场活跃度提升。</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为粮食种植、房产租赁经纪、磷肥及磷化工，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FINAL_SUBMISSION/02_市场观察/02_市场观察记录.xlsx
+++ b/FINAL_SUBMISSION/02_市场观察/02_市场观察记录.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -521,7 +521,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>9383亿元</t>
+          <t>20307亿元（沪+深）</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -531,12 +531,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>海洋捕捞(4.49%)、肉鸡养殖(4.45%)、房地产综合服务(4.27%)、动物保健Ⅲ(4.27%)、动物保健Ⅱ(4.27%)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4548.05点（-0.10%），跌破20日均线；两市成交额约9383亿元，较前5日均量放大（前5日均值约9168亿元），市场活跃度提升。</t>
+          <t>沪深300收于4548.05点（-0.10%），跌破20日均线；两市成交额（沪+深）约20307亿元，较前5日均量放大（前5日均值约19632亿元），市场活跃度提升。</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>8979亿元</t>
+          <t>19460亿元（沪+深）</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>被动元件(4.42%)、半导体设备(4.4%)、其他养殖(4.36%)、激光设备(4.16%)、海洋捕捞(4.09%)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4575.02点（+0.59%），跌破20日均线；两市成交额约8979亿元，较前5日均量萎缩（前5日均值约9104亿元），市场情绪偏谨慎。</t>
+          <t>沪深300收于4575.02点（+0.59%），跌破20日均线；两市成交额（沪+深）约19460亿元，较前5日均量萎缩（前5日均值约19490亿元），市场情绪偏谨慎。</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9156亿元</t>
+          <t>19603亿元（沪+深）</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>油田服务(5.0%)、煤化工(4.89%)、油服工程(4.72%)、农产品加工(4.69%)、其他种植业(4.65%)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4558.74点（-0.36%），跌破20日均线；两市成交额约9156亿元，较前5日均量放大（前5日均值约8871亿元），市场活跃度提升。</t>
+          <t>沪深300收于4558.74点（-0.36%），跌破20日均线；两市成交额（沪+深）约19603亿元，较前5日均量放大（前5日均值约19120亿元），市场活跃度提升。</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -649,6 +649,110 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>3951.51（+0.28%）</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>13723.32（+0.15%）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4572.60（+0.30%）</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18556亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>教育运营及其他(6.03%)、其他种植业(5.96%)、橡胶助剂(5.46%)、通信线缆及配套(4.98%)、航海装备Ⅲ(4.67%)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>水务及水治理(-0.19%)、其他建材Ⅲ(-0.19%)、综合乘用车(-0.2%)、其他电源设备Ⅱ(-0.2%)、快递(-0.21%)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4572.60点（+0.30%），跌破20日均线；两市成交额（沪+深）约18556亿元，较前5日均量萎缩（前5日均值约18974亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为教育运营及其他、其他种植业、橡胶助剂，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>3934.40（-0.43%）</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>13617.67（-0.77%）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4548.39（-0.53%）</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16472亿元（沪+深）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>教育运营及其他(6.02%)、卫浴电器(4.87%)、其他饰品(4.72%)、玻纤制造(3.77%)、玻璃玻纤(2.53%)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>纺织服饰(-1.66%)、氯碱(-1.66%)、专用设备(-1.67%)、生活用纸(-1.67%)、工业金属(-1.67%)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>沪深300收于4548.39点（-0.53%），跌破20日均线；两市成交额（沪+深）约16471亿元，较前5日均量萎缩（前5日均值约19103亿元），市场情绪偏谨慎。</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>当日领涨板块为教育运营及其他、卫浴电器、其他饰品，与观察池重合度低，维持现有组合，等待评分触发。</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>个股业绩披露期业绩变脸风险；宏观消息面突发扰动</t>
         </is>

--- a/FINAL_SUBMISSION/02_市场观察/02_市场观察记录.xlsx
+++ b/FINAL_SUBMISSION/02_市场观察/02_市场观察记录.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16472亿元（沪+深）</t>
+          <t>16471亿元（沪+深）</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -739,12 +739,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>纺织服饰(-1.66%)、氯碱(-1.66%)、专用设备(-1.67%)、生活用纸(-1.67%)、工业金属(-1.67%)</t>
+          <t>其他养殖(-5.53%)、氮肥(-5.13%)、其他农产品加工(-5.03%)、复合肥(-4.9%)、种子(-4.82%)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>沪深300收于4548.39点（-0.53%），跌破20日均线；两市成交额（沪+深）约16471亿元，较前5日均量萎缩（前5日均值约19103亿元），市场情绪偏谨慎。</t>
+          <t>沪深300收于4548.39点（-0.53%），跌破20日均线；两市成交额约16471亿元，较前5日均量萎缩（前5日均值约19103亿元），市场情绪偏谨慎。</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
